--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:31</t>
+          <t>更新时间: 2026-09-13 12:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:50</t>
+          <t>更新时间: 2026-09-13 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:32</t>
+          <t>更新时间: 2026-09-13 15:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 15:31</t>
+          <t>更新时间: 2026-09-13 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 17:15</t>
+          <t>更新时间: 2026-09-14 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:38</t>
+          <t>更新时间: 2026-09-14 12:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 12:58</t>
+          <t>更新时间: 2026-09-14 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:36</t>
+          <t>更新时间: 2026-09-14 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 10:01</t>
+          <t>更新时间: 2026-09-15 12:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:56</t>
+          <t>更新时间: 2026-09-15 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:38</t>
+          <t>更新时间: 2026-09-15 15:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 15:53</t>
+          <t>更新时间: 2026-09-15 17:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 17:16</t>
+          <t>更新时间: 2026-09-16 09:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:46</t>
+          <t>更新时间: 2026-09-16 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:51</t>
+          <t>更新时间: 2026-09-16 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:32</t>
+          <t>更新时间: 2026-09-16 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:09</t>
+          <t>更新时间: 2026-09-17 09:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:49</t>
+          <t>更新时间: 2026-09-17 12:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:38</t>
+          <t>更新时间: 2026-09-17 15:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:49</t>
+          <t>更新时间: 2026-09-17 17:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:36</t>
+          <t>更新时间: 2026-09-18 12:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:45</t>
+          <t>更新时间: 2026-09-18 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:26</t>
+          <t>更新时间: 2026-09-18 15:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:39</t>
+          <t>更新时间: 2026-09-19 12:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:39</t>
+          <t>更新时间: 2026-09-19 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:22</t>
+          <t>更新时间: 2026-09-19 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:39</t>
+          <t>更新时间: 2026-09-20 09:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:42</t>
+          <t>更新时间: 2026-09-20 12:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:55</t>
+          <t>更新时间: 2026-09-20 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:35</t>
+          <t>更新时间: 2026-09-20 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:37</t>
+          <t>更新时间: 2026-09-21 12:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:44</t>
+          <t>更新时间: 2026-09-21 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 17:44</t>
+          <t>更新时间: 2026-09-22 10:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 10:00</t>
+          <t>更新时间: 2026-09-22 12:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:58</t>
+          <t>更新时间: 2026-09-22 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:41</t>
+          <t>更新时间: 2026-09-22 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 15:48</t>
+          <t>更新时间: 2026-09-22 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 17:09</t>
+          <t>更新时间: 2026-09-23 09:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:54</t>
+          <t>更新时间: 2026-09-23 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:24</t>
+          <t>更新时间: 2026-09-23 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:50</t>
+          <t>更新时间: 2026-09-24 12:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:54</t>
+          <t>更新时间: 2026-09-24 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:42</t>
+          <t>更新时间: 2026-09-24 15:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 10:00</t>
+          <t>更新时间: 2026-09-25 12:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:59</t>
+          <t>更新时间: 2026-09-25 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:40</t>
+          <t>更新时间: 2026-09-25 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:27</t>
+          <t>更新时间: 2026-09-26 10:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 10:03</t>
+          <t>更新时间: 2026-09-26 13:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:00</t>
+          <t>更新时间: 2026-09-26 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:43</t>
+          <t>更新时间: 2026-09-26 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:51</t>
+          <t>更新时间: 2026-09-26 17:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 17:13</t>
+          <t>更新时间: 2026-09-27 09:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:54</t>
+          <t>更新时间: 2026-09-27 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:20</t>
+          <t>更新时间: 2026-09-27 14:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:03</t>
+          <t>更新时间: 2026-09-27 16:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:21</t>
+          <t>更新时间: 2026-09-27 17:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:52</t>
+          <t>更新时间: 2026-09-28 10:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:08</t>
+          <t>更新时间: 2026-09-28 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:26</t>
+          <t>更新时间: 2026-09-28 14:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:11</t>
+          <t>更新时间: 2026-09-28 16:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:47</t>
+          <t>更新时间: 2026-09-28 18:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:41</t>
+          <t>更新时间: 2026-09-29 10:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:55</t>
+          <t>更新时间: 2026-09-29 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:28</t>
+          <t>更新时间: 2026-09-29 16:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:43</t>
+          <t>更新时间: 2026-09-29 18:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:28</t>
+          <t>更新时间: 2026-09-30 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:32</t>
+          <t>更新时间: 2026-09-30 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:34</t>
+          <t>更新时间: 2026-09-30 14:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:12</t>
+          <t>更新时间: 2026-09-30 16:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:20</t>
+          <t>更新时间: 2026-10-01 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:36</t>
+          <t>更新时间: 2026-10-01 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:57</t>
+          <t>更新时间: 2026-10-01 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:43</t>
+          <t>更新时间: 2026-10-01 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:06</t>
+          <t>更新时间: 2026-10-01 18:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:47</t>
+          <t>更新时间: 2026-10-02 10:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:43</t>
+          <t>更新时间: 2026-10-02 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:40</t>
+          <t>更新时间: 2026-10-02 14:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:31</t>
+          <t>更新时间: 2026-10-02 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:30</t>
+          <t>更新时间: 2026-10-03 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:20</t>
+          <t>更新时间: 2026-10-03 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:56</t>
+          <t>更新时间: 2026-10-03 16:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:19</t>
+          <t>更新时间: 2026-10-03 17:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:43</t>
+          <t>更新时间: 2026-10-04 11:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:04</t>
+          <t>更新时间: 2026-10-04 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:56</t>
+          <t>更新时间: 2026-10-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:33</t>
+          <t>更新时间: 2026-10-04 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:33</t>
+          <t>更新时间: 2026-10-04 18:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 18:27</t>
+          <t>更新时间: 2026-10-05 10:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:30</t>
+          <t>更新时间: 2026-10-05 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 13:44</t>
+          <t>更新时间: 2026-10-05 14:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:27</t>
+          <t>更新时间: 2026-10-05 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 17:15</t>
+          <t>更新时间: 2026-10-05 19:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 19:15</t>
+          <t>更新时间: 2026-10-06 11:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 11:26</t>
+          <t>更新时间: 2026-10-06 14:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:23</t>
+          <t>更新时间: 2026-10-06 15:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:03</t>
+          <t>更新时间: 2026-10-06 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 17:07</t>
+          <t>更新时间: 2026-10-06 19:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 19:05</t>
+          <t>更新时间: 2026-10-07 10:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:56</t>
+          <t>更新时间: 2026-10-07 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:02</t>
+          <t>更新时间: 2026-10-07 14:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:45</t>
+          <t>更新时间: 2026-10-07 16:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 16:54</t>
+          <t>更新时间: 2026-10-07 18:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 11:04</t>
+          <t>更新时间: 2026-10-08 14:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:07</t>
+          <t>更新时间: 2026-10-08 14:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:54</t>
+          <t>更新时间: 2026-10-08 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 17:10</t>
+          <t>更新时间: 2026-10-08 19:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 19:11</t>
+          <t>更新时间: 2026-10-09 11:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 11:17</t>
+          <t>更新时间: 2026-10-09 14:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:11</t>
+          <t>更新时间: 2026-10-09 15:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:03</t>
+          <t>更新时间: 2026-10-09 17:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 17:18</t>
+          <t>更新时间: 2026-10-09 19:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 19:10</t>
+          <t>更新时间: 2026-10-10 10:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:53</t>
+          <t>更新时间: 2026-10-10 13:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 13:55</t>
+          <t>更新时间: 2026-10-10 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:34</t>
+          <t>更新时间: 2026-10-10 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 16:40</t>
+          <t>更新时间: 2026-10-10 18:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 18:28</t>
+          <t>更新时间: 2026-10-11 10:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 10:23</t>
+          <t>更新时间: 2026-10-11 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 13:49</t>
+          <t>更新时间: 2026-10-11 14:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:42</t>
+          <t>更新时间: 2026-10-11 17:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 17:04</t>
+          <t>更新时间: 2026-10-11 18:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 18:39</t>
+          <t>更新时间: 2026-10-12 10:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 10:49</t>
+          <t>更新时间: 2026-10-12 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:01</t>
+          <t>更新时间: 2026-10-12 14:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:49</t>
+          <t>更新时间: 2026-10-12 17:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 17:26</t>
+          <t>更新时间: 2026-10-12 19:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 12:02</t>
+          <t>更新时间: 2026-10-13 14:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 14:48</t>
+          <t>更新时间: 2026-10-13 15:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:15</t>
+          <t>更新时间: 2026-10-13 17:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 17:34</t>
+          <t>更新时间: 2026-10-13 19:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 19:30</t>
+          <t>更新时间: 2026-10-14 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 10:19</t>
+          <t>更新时间: 2026-10-14 12:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 12:55</t>
+          <t>更新时间: 2026-10-14 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:40</t>
+          <t>更新时间: 2026-10-14 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 15:48</t>
+          <t>更新时间: 2026-10-14 17:21</t>
         </is>
       </c>
     </row>
